--- a/data/excel/usuarios.xlsx
+++ b/data/excel/usuarios.xlsx
@@ -76,7 +76,64 @@
     <x:t>2026-06-30T18:08:21.4150441Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-01T03:39:08.1791847Z</x:t>
+    <x:t>2026-07-08T12:43:50.7047746Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0c3f83fc-b1f1-43e9-88ab-433765280bcf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bod1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bod1@test.cl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bodeguero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$BTj4dIiVpcyHBApy2jacmA==$0kBhHZKvnRboec6hCCdSFpuGySZwBCkCplsY75bsUIY=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:03:01.2047719Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:23.3604152Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e4447694-c49f-456f-abb0-35a9de1ecfa4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>con1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>con1@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>consulta_faena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$o71n0suFA+cuZ+0L+wf5kw==$AObgtJA3rM1lKLryzvKSnwe5Egao0q1Xvvli7YysyTE=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:16.3931216Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3ad6aace-1fa6-416a-bf09-6b3b30bbc257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ger1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ger1@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gerencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$tPJvHIt/tpGZ9Yj/RCOCAw==$f3XBK1i0MLPro1dRb6RoxkvtRMwFQ/d8tW2kqh366QE=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:05:59.8124353Z</x:t>
   </x:si>
   <x:si>
     <x:t>dbdcfa8d-b82b-464b-8c5e-7def74e86122</x:t>
@@ -100,7 +157,79 @@
     <x:t>2026-06-30T21:30:54.9277150Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-30T21:31:12.5663279Z</x:t>
+    <x:t>2026-07-08T17:58:10.4930433Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9ac69b51-fe10-40c2-b52d-fb957af6e993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>plani1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>plani1@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>planificador</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$YWEuLVwxHEGo6FlX0tzHoQ==$7dN4IfaS9ctASFvOWwlkfdKTxOS1PLnD0qDqodWz9nA=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:07:19.1430201Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>866e5098-0afe-4069-8acb-ccf90d054722</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_b1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_b1@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>supervisor_bodega</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$XFAkYBUO+ofp5pMKr43mvQ==$bPfFwCn8ofNgLpLHp/pOdEDHEr1MNBo4CX0QGAqKVig=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:08:11.8675578Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>589f4e25-1197-4a91-b06d-68c963f7db4b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_m1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sup_m1@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>supervisor_mantenimiento</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$cc2Zg3/KhDFv4m8BJ4U76g==$zY7JdGjWn0ne7auogLawPQT3gRnmQxJTEkx4pSmhlsM=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:09:06.4526648Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a9a0b7c8-87e8-4ce6-ad0b-777b2d733883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tec@test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tecnico</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PBKDF2-SHA256$100000$4ngTIRUet6ZSW4/tCnyxYA==$8SxX9VArso4fYjNM4ornLw1OUiC3UqeJzCnCFoHsy+w=</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T18:09:36.9697161Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -466,16 +595,16 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K3"/>
+  <x:dimension ref="A1:K10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="37.996339" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="21.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="103.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="104.567768" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="7.424911" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="25.710625" style="0" customWidth="1"/>
     <x:col min="10" max="11" width="28.282054" style="0" customWidth="1"/>
@@ -574,13 +703,219 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
+      <x:c r="K3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="0" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
